--- a/artfynd/A 41123-2024 artfynd.xlsx
+++ b/artfynd/A 41123-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272169</v>
+        <v>121272177</v>
       </c>
       <c r="B2" t="n">
-        <v>105176</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346680</v>
+        <v>346698</v>
       </c>
       <c r="R2" t="n">
-        <v>6560258</v>
+        <v>6560268</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272177</v>
+        <v>121272169</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>105186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346698</v>
+        <v>346680</v>
       </c>
       <c r="R3" t="n">
-        <v>6560268</v>
+        <v>6560258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41123-2024 artfynd.xlsx
+++ b/artfynd/A 41123-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272177</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121272169</v>
       </c>
       <c r="B3" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41123-2024 artfynd.xlsx
+++ b/artfynd/A 41123-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272177</v>
+        <v>121272169</v>
       </c>
       <c r="B2" t="n">
-        <v>100360</v>
+        <v>105200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346698</v>
+        <v>346680</v>
       </c>
       <c r="R2" t="n">
-        <v>6560268</v>
+        <v>6560258</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272169</v>
+        <v>121272177</v>
       </c>
       <c r="B3" t="n">
-        <v>105199</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346680</v>
+        <v>346698</v>
       </c>
       <c r="R3" t="n">
-        <v>6560258</v>
+        <v>6560268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41123-2024 artfynd.xlsx
+++ b/artfynd/A 41123-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272169</v>
+        <v>121272177</v>
       </c>
       <c r="B2" t="n">
-        <v>105200</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346680</v>
+        <v>346698</v>
       </c>
       <c r="R2" t="n">
-        <v>6560258</v>
+        <v>6560268</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272177</v>
+        <v>121272169</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>105203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346698</v>
+        <v>346680</v>
       </c>
       <c r="R3" t="n">
-        <v>6560268</v>
+        <v>6560258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41123-2024 artfynd.xlsx
+++ b/artfynd/A 41123-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121272177</v>
+        <v>121272169</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>105209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346698</v>
+        <v>346680</v>
       </c>
       <c r="R2" t="n">
-        <v>6560268</v>
+        <v>6560258</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121272169</v>
+        <v>121272177</v>
       </c>
       <c r="B3" t="n">
-        <v>105203</v>
+        <v>100370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346680</v>
+        <v>346698</v>
       </c>
       <c r="R3" t="n">
-        <v>6560258</v>
+        <v>6560268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41123-2024 artfynd.xlsx
+++ b/artfynd/A 41123-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121272169</v>
       </c>
       <c r="B2" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121272177</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
